--- a/static/plot/nozzle_report.xlsx
+++ b/static/plot/nozzle_report.xlsx
@@ -438,36 +438,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Required Thrust       : 10000.0 N</t>
+          <t>Required Thrust       : 2000.0 N</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nozzle Area Ratio     : 19.6650</t>
+          <t>Nozzle Area Ratio     : 12.4724</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Required Mass flow    : 3.5285 kg/s</t>
+          <t>Required Mass flow    : 0.8545 kg/s</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stagnation Density    : 4.6623 kg/m³</t>
+          <t>Stagnation Density    : 3.4843 kg/m³</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chamber Diameter      : 110.79 mm</t>
+          <t>Chamber Diameter      : 68.13 mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Throat Velocity       : 1135.3614 m/s</t>
+          <t>Throat Velocity       : 972.7920 m/s</t>
         </is>
       </c>
     </row>
@@ -479,50 +479,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Throat Density        : 2.9012 kg/m³</t>
+          <t>Throat Density        : 2.1682 kg/m³</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Convergent Length     : 63.97 mm</t>
+          <t>Convergent Length     : 39.34 mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exit Mach number      : 3.8307</t>
+          <t>Exit Mach number      : 3.4980</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Throat Diameter       : 36.93 mm</t>
+          <t>Throat Diameter       : 22.71 mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>General mass flow     : 0.1794 kg/s</t>
+          <t>General mass flow     : 0.0685 kg/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Divergent Length      : 236.69 mm</t>
+          <t>Divergent Length      : 107.29 mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Choked mass flow      : 3.5285 kg/s</t>
+          <t>Choked mass flow      : 0.8545 kg/s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Exit Diameter         : 163.77 mm</t>
+          <t>Exit Diameter         : 80.21 mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -534,40 +534,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Nozzle Length   : 356.21 mm</t>
+          <t>Total Nozzle Length   : 202.18 mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Exit Temperature      : 1262.3450 K</t>
+          <t>Exit Temperature      : 1278.7869 K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exit Velocity         : 2834.0507 m/s</t>
+          <t>Exit Velocity         : 2340.6789 m/s</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>Specific Impulse      : 288.9927 S</t>
+          <t>Specific Impulse      : 238.6828 S</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>Exit Mass flow rate   : 3.5285 kg/s</t>
+          <t>Exit Mass flow rate   : 0.8545 kg/s</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>Final Thrust          : 10000.0000 N</t>
+          <t>Final Thrust          : 2000.0000 N</t>
         </is>
       </c>
     </row>

--- a/static/plot/nozzle_report.xlsx
+++ b/static/plot/nozzle_report.xlsx
@@ -438,36 +438,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Required Thrust       : 2000.0 N</t>
+          <t>Required Thrust       : 10000.0 N</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nozzle Area Ratio     : 12.4724</t>
+          <t>Nozzle Area Ratio     : 19.6650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Required Mass flow    : 0.8545 kg/s</t>
+          <t>Required Mass flow    : 3.5285 kg/s</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stagnation Density    : 3.4843 kg/m³</t>
+          <t>Stagnation Density    : 4.6623 kg/m³</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chamber Diameter      : 68.13 mm</t>
+          <t>Chamber Diameter      : 110.79 mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Throat Velocity       : 972.7920 m/s</t>
+          <t>Throat Velocity       : 1135.3614 m/s</t>
         </is>
       </c>
     </row>
@@ -479,50 +479,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Throat Density        : 2.1682 kg/m³</t>
+          <t>Throat Density        : 2.9012 kg/m³</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Convergent Length     : 39.34 mm</t>
+          <t>Convergent Length     : 63.97 mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exit Mach number      : 3.4980</t>
+          <t>Exit Mach number      : 3.8307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Throat Diameter       : 22.71 mm</t>
+          <t>Throat Diameter       : 36.93 mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>General mass flow     : 0.0685 kg/s</t>
+          <t>General mass flow     : 0.1794 kg/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Divergent Length      : 107.29 mm</t>
+          <t>Divergent Length      : 236.69 mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Choked mass flow      : 0.8545 kg/s</t>
+          <t>Choked mass flow      : 3.5285 kg/s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Exit Diameter         : 80.21 mm</t>
+          <t>Exit Diameter         : 163.77 mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -534,40 +534,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Nozzle Length   : 202.18 mm</t>
+          <t>Total Nozzle Length   : 356.21 mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Exit Temperature      : 1278.7869 K</t>
+          <t>Exit Temperature      : 1262.3450 K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exit Velocity         : 2340.6789 m/s</t>
+          <t>Exit Velocity         : 2834.0507 m/s</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>Specific Impulse      : 238.6828 S</t>
+          <t>Specific Impulse      : 288.9927 S</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>Exit Mass flow rate   : 0.8545 kg/s</t>
+          <t>Exit Mass flow rate   : 3.5285 kg/s</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>Final Thrust          : 2000.0000 N</t>
+          <t>Final Thrust          : 10000.0000 N</t>
         </is>
       </c>
     </row>
